--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484528_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484528_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.121</v>
+        <v>5.679</v>
       </c>
       <c r="E2" t="n">
-        <v>4.721</v>
+        <v>4.2542</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4</v>
+        <v>1.4248</v>
       </c>
       <c r="G2" t="n">
         <v>7.0412</v>
@@ -610,13 +610,13 @@
         <v>2.1991</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8966</v>
+        <v>0.4545</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0234</v>
+        <v>0.5566</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1268</v>
+        <v>-0.102</v>
       </c>
       <c r="V2" t="n">
         <v>-1.267</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4092</v>
+        <v>4.4322</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2725</v>
+        <v>4.9735</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8633</v>
+        <v>-0.5413</v>
       </c>
       <c r="G3" t="n">
         <v>4.7262</v>
@@ -688,13 +688,13 @@
         <v>2.5656</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.2333</v>
+        <v>-0.2102</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8273</v>
+        <v>-0.1263</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.406</v>
+        <v>-0.0839</v>
       </c>
       <c r="V3" t="n">
         <v>-0.6335</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. DIAGNE</t>
+          <t>A. ALBA GONZALEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0372</v>
+        <v>3.1372</v>
       </c>
       <c r="E4" t="n">
-        <v>5.8294</v>
+        <v>2.9105</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.7921</v>
+        <v>0.2266</v>
       </c>
       <c r="G4" t="n">
-        <v>4.0974</v>
+        <v>3.7049</v>
       </c>
       <c r="H4" t="n">
-        <v>5.0368</v>
+        <v>1.7497</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.9394</v>
+        <v>1.9552</v>
       </c>
       <c r="J4" t="n">
-        <v>5.5861</v>
+        <v>5.5891</v>
       </c>
       <c r="K4" t="n">
-        <v>5.8521</v>
+        <v>3.3129</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.266</v>
+        <v>2.2762</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.4887</v>
+        <v>-1.8842</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8152</v>
+        <v>-1.5632</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6735</v>
+        <v>-0.321</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.2828</v>
+        <v>-1.6493</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.9321</v>
+        <v>-3.8484</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6493</v>
+        <v>2.1991</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8353</v>
+        <v>0.1157</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9322</v>
+        <v>0.204</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0969</v>
+        <v>-0.0883</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.6127</v>
+        <v>0.9658</v>
       </c>
       <c r="W4" t="n">
-        <v>2.2432</v>
+        <v>0.9658</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.8559</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. ALBA GONZALEZ</t>
+          <t>E. DIAGNE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.7335</v>
+        <v>2.7246</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2096</v>
+        <v>5.4176</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5239</v>
+        <v>-2.693</v>
       </c>
       <c r="G5" t="n">
-        <v>3.7049</v>
+        <v>4.0974</v>
       </c>
       <c r="H5" t="n">
-        <v>1.7497</v>
+        <v>5.0368</v>
       </c>
       <c r="I5" t="n">
-        <v>1.9552</v>
+        <v>-0.9394</v>
       </c>
       <c r="J5" t="n">
-        <v>5.5891</v>
+        <v>5.5861</v>
       </c>
       <c r="K5" t="n">
-        <v>3.3129</v>
+        <v>5.8521</v>
       </c>
       <c r="L5" t="n">
-        <v>2.2762</v>
+        <v>-0.266</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.8842</v>
+        <v>-1.4887</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.5632</v>
+        <v>-0.8152</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.321</v>
+        <v>-0.6735</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.6493</v>
+        <v>-1.2828</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.8484</v>
+        <v>-2.9321</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1991</v>
+        <v>1.6493</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.288</v>
+        <v>0.5226</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.497</v>
+        <v>0.5204</v>
       </c>
       <c r="U5" t="n">
-        <v>0.209</v>
+        <v>0.0022</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9658</v>
+        <v>-0.6127</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9658</v>
+        <v>2.2432</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-2.8559</v>
       </c>
     </row>
     <row r="6">
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4699</v>
+        <v>0.5634</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2845</v>
+        <v>-1.191</v>
       </c>
       <c r="F6" t="n">
         <v>1.7544</v>
@@ -922,10 +922,10 @@
         <v>1.0995</v>
       </c>
       <c r="S6" t="n">
-        <v>1.172</v>
+        <v>0.2655</v>
       </c>
       <c r="T6" t="n">
-        <v>1.4088</v>
+        <v>0.5023</v>
       </c>
       <c r="U6" t="n">
         <v>-0.2368</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.7307</v>
+        <v>-1.2281</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.8534</v>
+        <v>-3.2765</v>
       </c>
       <c r="F7" t="n">
-        <v>2.1227</v>
+        <v>2.0483</v>
       </c>
       <c r="G7" t="n">
         <v>-0.6195000000000001</v>
@@ -1000,13 +1000,13 @@
         <v>2.0158</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0013</v>
+        <v>-0.4987</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5694</v>
+        <v>0.0076</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4319</v>
+        <v>-0.5062</v>
       </c>
       <c r="V7" t="n">
         <v>0.6231</v>
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.4272</v>
+        <v>-3.276</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.3872</v>
+        <v>-2.236</v>
       </c>
       <c r="F8" t="n">
         <v>-1.04</v>
@@ -1078,10 +1078,10 @@
         <v>0.733</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6961000000000001</v>
+        <v>-0.5449000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3303</v>
+        <v>-0.1791</v>
       </c>
       <c r="U8" t="n">
         <v>-0.3658</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.1098</v>
+        <v>-3.6591</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.6986</v>
+        <v>-3.1489</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4111</v>
+        <v>-0.5102</v>
       </c>
       <c r="G9" t="n">
         <v>-2.3038</v>
@@ -1156,13 +1156,13 @@
         <v>1.6493</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1279</v>
+        <v>-0.6772</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7896</v>
+        <v>-0.2398</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3383</v>
+        <v>-0.4374</v>
       </c>
       <c r="V9" t="n">
         <v>-0.3115</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.2398</v>
+        <v>-4.0088</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.515</v>
+        <v>-3.3087</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7248</v>
+        <v>-0.7000999999999999</v>
       </c>
       <c r="G10" t="n">
         <v>-0.2693</v>
@@ -1234,13 +1234,13 @@
         <v>1.4661</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6615</v>
+        <v>-0.4304</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1847</v>
+        <v>0.0215</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4767</v>
+        <v>-0.4519</v>
       </c>
       <c r="V10" t="n">
         <v>-0.0104</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>3.263300000000001</v>
+        <v>4.364400000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>3.293799999999998</v>
+        <v>4.394699999999998</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0303000000000001</v>
+        <v>-0.03050000000000042</v>
       </c>
       <c r="G11" t="n">
         <v>13.3026</v>
@@ -1312,13 +1312,13 @@
         <v>15.5768</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.1042</v>
+        <v>-1.0031</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1661000000000002</v>
+        <v>1.2672</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.2702</v>
+        <v>-2.2701</v>
       </c>
       <c r="V11" t="n">
         <v>0.3115000000000003</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>N. CARPITELLI</t>
+          <t>L. ALBEROLA GUILLOT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.9151</v>
+        <v>4.7325</v>
       </c>
       <c r="E12" t="n">
-        <v>3.0174</v>
+        <v>2.9588</v>
       </c>
       <c r="F12" t="n">
-        <v>1.8976</v>
+        <v>1.7737</v>
       </c>
       <c r="G12" t="n">
-        <v>3.0715</v>
+        <v>0.9568</v>
       </c>
       <c r="H12" t="n">
-        <v>1.2861</v>
+        <v>-1.5182</v>
       </c>
       <c r="I12" t="n">
-        <v>1.7853</v>
+        <v>2.475</v>
       </c>
       <c r="J12" t="n">
-        <v>4.2929</v>
+        <v>2.3645</v>
       </c>
       <c r="K12" t="n">
-        <v>2.2509</v>
+        <v>0.402</v>
       </c>
       <c r="L12" t="n">
-        <v>2.042</v>
+        <v>1.9625</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.2214</v>
+        <v>-1.4077</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.9647</v>
+        <v>-1.9202</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.2567</v>
+        <v>0.5125</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.733</v>
+        <v>1.8326</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.8484</v>
+        <v>-1.0995</v>
       </c>
       <c r="R12" t="n">
-        <v>3.1154</v>
+        <v>2.9321</v>
       </c>
       <c r="S12" t="n">
-        <v>3.2641</v>
+        <v>1.3741</v>
       </c>
       <c r="T12" t="n">
-        <v>2.8741</v>
+        <v>1.0604</v>
       </c>
       <c r="U12" t="n">
-        <v>0.39</v>
+        <v>0.3137</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.6875</v>
+        <v>0.5691000000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.3011</v>
+        <v>0.6335</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.3863</v>
+        <v>-0.0644</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>L. ALBEROLA GUILLOT</t>
+          <t>N. CARPITELLI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.5461</v>
+        <v>3.4232</v>
       </c>
       <c r="E13" t="n">
-        <v>2.5741</v>
+        <v>1.5751</v>
       </c>
       <c r="F13" t="n">
-        <v>1.9719</v>
+        <v>1.8481</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9568</v>
+        <v>3.0715</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.5182</v>
+        <v>1.2861</v>
       </c>
       <c r="I13" t="n">
-        <v>2.475</v>
+        <v>1.7853</v>
       </c>
       <c r="J13" t="n">
-        <v>2.3645</v>
+        <v>4.2929</v>
       </c>
       <c r="K13" t="n">
-        <v>0.402</v>
+        <v>2.2509</v>
       </c>
       <c r="L13" t="n">
-        <v>1.9625</v>
+        <v>2.042</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.4077</v>
+        <v>-1.2214</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.9202</v>
+        <v>-0.9647</v>
       </c>
       <c r="O13" t="n">
-        <v>0.5125</v>
+        <v>-0.2567</v>
       </c>
       <c r="P13" t="n">
-        <v>1.8326</v>
+        <v>-0.733</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.0995</v>
+        <v>-3.8484</v>
       </c>
       <c r="R13" t="n">
-        <v>2.9321</v>
+        <v>3.1154</v>
       </c>
       <c r="S13" t="n">
-        <v>1.1876</v>
+        <v>1.7722</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6757</v>
+        <v>1.4318</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5119</v>
+        <v>0.3405</v>
       </c>
       <c r="V13" t="n">
-        <v>0.5691000000000001</v>
+        <v>-0.6875</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6335</v>
+        <v>-0.3011</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.0644</v>
+        <v>-0.3863</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.2014</v>
+        <v>3.0201</v>
       </c>
       <c r="E14" t="n">
-        <v>1.0762</v>
+        <v>1.8454</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1252</v>
+        <v>1.1747</v>
       </c>
       <c r="G14" t="n">
         <v>0.2241</v>
@@ -1546,13 +1546,13 @@
         <v>2.5656</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2784</v>
+        <v>0.5403</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3861</v>
+        <v>0.3831</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1077</v>
+        <v>0.1572</v>
       </c>
       <c r="V14" t="n">
         <v>-0.1267</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. ALVAREZ LABRADOR</t>
+          <t>G. GARCIA BURGOS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.7927</v>
+        <v>2.1822</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2649</v>
+        <v>3.5368</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5278</v>
+        <v>-1.3546</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.8208</v>
+        <v>0.6798</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.2504</v>
+        <v>0.4717</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4297</v>
+        <v>0.2081</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.0571</v>
+        <v>2.5118</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.1087</v>
+        <v>2.3034</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0515</v>
+        <v>0.2084</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2364</v>
+        <v>-1.832</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.1418</v>
+        <v>-1.8317</v>
       </c>
       <c r="O15" t="n">
-        <v>1.3781</v>
+        <v>-0.0003</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3665</v>
+        <v>1.0995</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.8326</v>
+        <v>-1.0995</v>
       </c>
       <c r="R15" t="n">
         <v>2.1991</v>
       </c>
       <c r="S15" t="n">
-        <v>0.98</v>
+        <v>1.0903</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6207</v>
+        <v>0.8367</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3593</v>
+        <v>0.2536</v>
       </c>
       <c r="V15" t="n">
-        <v>1.267</v>
+        <v>-0.6875</v>
       </c>
       <c r="W15" t="n">
-        <v>2.5339</v>
+        <v>1.2878</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.267</v>
+        <v>-1.9753</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. GARCIA BURGOS</t>
+          <t>P. ALVAREZ LABRADOR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5339</v>
+        <v>1.8291</v>
       </c>
       <c r="E16" t="n">
-        <v>2.8637</v>
+        <v>0.1688</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.3298</v>
+        <v>1.6603</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6798</v>
+        <v>-0.8208</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4717</v>
+        <v>-2.2504</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2081</v>
+        <v>1.4297</v>
       </c>
       <c r="J16" t="n">
-        <v>2.5118</v>
+        <v>-1.0571</v>
       </c>
       <c r="K16" t="n">
-        <v>2.3034</v>
+        <v>-1.1087</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2084</v>
+        <v>0.0515</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.832</v>
+        <v>0.2364</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.8317</v>
+        <v>-1.1418</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0003</v>
+        <v>1.3781</v>
       </c>
       <c r="P16" t="n">
-        <v>1.0995</v>
+        <v>0.3665</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0995</v>
+        <v>-1.8326</v>
       </c>
       <c r="R16" t="n">
         <v>2.1991</v>
       </c>
       <c r="S16" t="n">
-        <v>0.442</v>
+        <v>1.0164</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1637</v>
+        <v>0.5245</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2783</v>
+        <v>0.4919</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6875</v>
+        <v>1.267</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2878</v>
+        <v>2.5339</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.9753</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="17">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3543</v>
+        <v>0.4782</v>
       </c>
       <c r="E18" t="n">
         <v>-0.2019</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5563</v>
+        <v>0.6801</v>
       </c>
       <c r="G18" t="n">
         <v>-0.3694</v>
@@ -1858,13 +1858,13 @@
         <v>0.733</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3209</v>
+        <v>-0.197</v>
       </c>
       <c r="T18" t="n">
         <v>-0.3303</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0094</v>
+        <v>0.1333</v>
       </c>
       <c r="V18" t="n">
         <v>0.3115</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0902</v>
+        <v>0.0337</v>
       </c>
       <c r="E20" t="n">
         <v>-1.2248</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1346</v>
+        <v>1.2585</v>
       </c>
       <c r="G20" t="n">
         <v>-2.6183</v>
@@ -2014,13 +2014,13 @@
         <v>2.9321</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1369</v>
+        <v>0.2608</v>
       </c>
       <c r="T20" t="n">
         <v>0.31</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1731</v>
+        <v>-0.0492</v>
       </c>
       <c r="V20" t="n">
         <v>0.5587</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.912</v>
+        <v>-1.3709</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5588</v>
+        <v>0.1742</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4708</v>
+        <v>-1.5452</v>
       </c>
       <c r="G21" t="n">
         <v>-1.7969</v>
@@ -2092,13 +2092,13 @@
         <v>0.733</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1518</v>
+        <v>-0.3071</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1086</v>
+        <v>-0.276</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0432</v>
+        <v>-0.0311</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4027</v>
+        <v>-2.6023</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4348</v>
+        <v>-1.9156</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9679</v>
+        <v>-0.6867</v>
       </c>
       <c r="G22" t="n">
         <v>-3.5931</v>
@@ -2170,13 +2170,13 @@
         <v>1.8326</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4554</v>
+        <v>0.2559</v>
       </c>
       <c r="T22" t="n">
-        <v>0.6026</v>
+        <v>0.1218</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1471</v>
+        <v>0.134</v>
       </c>
       <c r="V22" t="n">
         <v>1.6512</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.8544</v>
+        <v>-3.3373</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.1919</v>
+        <v>-0.8073</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.6626</v>
+        <v>-2.53</v>
       </c>
       <c r="G23" t="n">
         <v>-1.2409</v>
@@ -2248,13 +2248,13 @@
         <v>1.6493</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1633</v>
+        <v>-0.6461</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0098</v>
+        <v>-0.6252</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1535</v>
+        <v>-0.021</v>
       </c>
       <c r="V23" t="n">
         <v>-1.267</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.2653</v>
+        <v>-3.7889</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.0581</v>
+        <v>-0.962</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.2072</v>
+        <v>-2.8269</v>
       </c>
       <c r="G24" t="n">
         <v>-3.4838</v>
@@ -2326,13 +2326,13 @@
         <v>1.2828</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.4204</v>
+        <v>-0.944</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6244</v>
+        <v>-0.5283</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.796</v>
+        <v>-0.4157</v>
       </c>
       <c r="V24" t="n">
         <v>-0.6439</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.3574</v>
+        <v>-7.8562</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.4886</v>
+        <v>-6.3925</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.8688</v>
+        <v>-1.4638</v>
       </c>
       <c r="G25" t="n">
         <v>-5.5868</v>
@@ -2404,13 +2404,13 @@
         <v>1.6493</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.3308</v>
+        <v>-0.8296</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.7345</v>
+        <v>-0.6384</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.5962</v>
+        <v>-0.1912</v>
       </c>
       <c r="V25" t="n">
         <v>-1.2566</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.263199999999999</v>
+        <v>-1.981300000000002</v>
       </c>
       <c r="E26" t="n">
-        <v>0.03029999999999866</v>
+        <v>0.03030000000000221</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.293700000000001</v>
+        <v>-2.011799999999999</v>
       </c>
       <c r="G26" t="n">
         <v>-13.3025</v>
@@ -2461,7 +2461,7 @@
         <v>6.7784</v>
       </c>
       <c r="L26" t="n">
-        <v>0.4834000000000005</v>
+        <v>0.4834000000000001</v>
       </c>
       <c r="M26" t="n">
         <v>-20.5641</v>
@@ -2476,19 +2476,19 @@
         <v>8.246400000000001</v>
       </c>
       <c r="Q26" t="n">
-        <v>-15.57689999999999</v>
+        <v>-15.5769</v>
       </c>
       <c r="R26" t="n">
         <v>23.8234</v>
       </c>
       <c r="S26" t="n">
-        <v>2.104</v>
+        <v>3.3862</v>
       </c>
       <c r="T26" t="n">
-        <v>2.270299999999999</v>
+        <v>2.2701</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.1661</v>
+        <v>1.116</v>
       </c>
       <c r="V26" t="n">
         <v>-0.3116999999999995</v>
